--- a/sources/king_step10.xlsx
+++ b/sources/king_step10.xlsx
@@ -1489,11 +1489,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AB14" t="inlineStr">
         <is>
           <t>67ff2023-6e37-4766-ab77-10e230c708b4</t>
@@ -1561,11 +1556,6 @@
           <t>3+4</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AB15" t="inlineStr">
         <is>
           <t>c4c3cd71-ed27-44df-a655-fb09f78b6be8</t>
@@ -1633,11 +1623,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AB16" t="inlineStr">
         <is>
           <t>f8794d93-a444-4657-859f-d2548700e248</t>
@@ -1703,11 +1688,6 @@
       <c r="W17" t="inlineStr">
         <is>
           <t>1+2</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">

--- a/sources/king_step10.xlsx
+++ b/sources/king_step10.xlsx
@@ -11040,12 +11040,12 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">

--- a/sources/king_step10.xlsx
+++ b/sources/king_step10.xlsx
@@ -1489,6 +1489,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>67ff2023-6e37-4766-ab77-10e230c708b4</t>
+        </is>
+      </c>
       <c r="AB14" t="inlineStr">
         <is>
           <t>67ff2023-6e37-4766-ab77-10e230c708b4</t>
@@ -1556,6 +1561,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>c4c3cd71-ed27-44df-a655-fb09f78b6be8</t>
+        </is>
+      </c>
       <c r="AB15" t="inlineStr">
         <is>
           <t>c4c3cd71-ed27-44df-a655-fb09f78b6be8</t>
@@ -1623,6 +1633,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>f8794d93-a444-4657-859f-d2548700e248</t>
+        </is>
+      </c>
       <c r="AB16" t="inlineStr">
         <is>
           <t>f8794d93-a444-4657-859f-d2548700e248</t>
@@ -1690,6 +1705,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>9821af5c-9a74-43da-8d33-7092f2b7ff7b</t>
+        </is>
+      </c>
       <c r="AB17" t="inlineStr">
         <is>
           <t>9821af5c-9a74-43da-8d33-7092f2b7ff7b</t>
@@ -1762,6 +1782,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
+        </is>
+      </c>
       <c r="AB18" t="inlineStr">
         <is>
           <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
@@ -1819,6 +1844,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>f8490fa0-7b1f-4f39-99ab-da6ae361ed20</t>
+        </is>
+      </c>
       <c r="AB19" t="inlineStr">
         <is>
           <t>f8490fa0-7b1f-4f39-99ab-da6ae361ed20</t>
@@ -1881,6 +1911,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>68f074ca-3602-4223-bca2-a6b2ec87ef2a</t>
+        </is>
+      </c>
       <c r="AB20" t="inlineStr">
         <is>
           <t>68f074ca-3602-4223-bca2-a6b2ec87ef2a</t>
@@ -1943,6 +1978,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>0176585b-588a-49e1-9572-4bdd7101f82a</t>
+        </is>
+      </c>
       <c r="AB21" t="inlineStr">
         <is>
           <t>0176585b-588a-49e1-9572-4bdd7101f82a</t>
@@ -2005,6 +2045,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>00ddf7e7-6010-4a77-9ae6-40ef2f2a707a</t>
+        </is>
+      </c>
       <c r="AB22" t="inlineStr">
         <is>
           <t>00ddf7e7-6010-4a77-9ae6-40ef2f2a707a</t>
@@ -2067,6 +2112,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>b6c23f31-cb1a-450f-9a17-e7cc5b124033</t>
+        </is>
+      </c>
       <c r="AB23" t="inlineStr">
         <is>
           <t>b6c23f31-cb1a-450f-9a17-e7cc5b124033</t>
@@ -2129,6 +2179,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>12308a0d-a04e-49ad-a92e-7b32fb03c49f</t>
+        </is>
+      </c>
       <c r="AB24" t="inlineStr">
         <is>
           <t>12308a0d-a04e-49ad-a92e-7b32fb03c49f</t>
@@ -2191,6 +2246,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>6c0cc2bf-f0ad-4b46-a1ff-2a7de8bdb37f</t>
+        </is>
+      </c>
       <c r="AB25" t="inlineStr">
         <is>
           <t>6c0cc2bf-f0ad-4b46-a1ff-2a7de8bdb37f</t>
@@ -2253,6 +2313,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>377bd68e-1783-43e2-8c72-05143260300a</t>
+        </is>
+      </c>
       <c r="AB26" t="inlineStr">
         <is>
           <t>377bd68e-1783-43e2-8c72-05143260300a</t>
@@ -2315,6 +2380,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>f57394c8-7aba-414b-af3e-d37941cae2e3</t>
+        </is>
+      </c>
       <c r="AB27" t="inlineStr">
         <is>
           <t>f57394c8-7aba-414b-af3e-d37941cae2e3</t>
@@ -2387,6 +2457,11 @@
           <t>The Counter Hit Stomach Smash is NOT a throw but is required before you can do the 2 throw follow ups.</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>b2d4546c-7d86-4fee-a8f7-dbe4e5857d92</t>
+        </is>
+      </c>
       <c r="AB28" t="inlineStr">
         <is>
           <t>b2d4546c-7d86-4fee-a8f7-dbe4e5857d92</t>
@@ -2444,6 +2519,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>829ce921-0e10-4ab2-bbbc-911f844eceef</t>
+        </is>
+      </c>
       <c r="AB29" t="inlineStr">
         <is>
           <t>829ce921-0e10-4ab2-bbbc-911f844eceef</t>
@@ -2506,6 +2586,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>db0aa370-9079-45e2-b39c-7472d8bae8a4</t>
+        </is>
+      </c>
       <c r="AB30" t="inlineStr">
         <is>
           <t>db0aa370-9079-45e2-b39c-7472d8bae8a4</t>
@@ -2578,6 +2663,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>6294b53d-e480-4df4-be9f-98a25b5e6a95</t>
+        </is>
+      </c>
       <c r="AB31" t="inlineStr">
         <is>
           <t>6294b53d-e480-4df4-be9f-98a25b5e6a95</t>
@@ -2645,6 +2735,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>16314dd7-17de-43e3-89e8-146678a228d1</t>
+        </is>
+      </c>
       <c r="AB32" t="inlineStr">
         <is>
           <t>16314dd7-17de-43e3-89e8-146678a228d1</t>
@@ -2712,6 +2807,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>ab65c71e-57c4-4826-b7e0-038c4501bdc6</t>
+        </is>
+      </c>
       <c r="AB33" t="inlineStr">
         <is>
           <t>ab65c71e-57c4-4826-b7e0-038c4501bdc6</t>
@@ -2774,6 +2874,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>fe0b77cb-f2dd-4ba4-b684-d4ecf9d4a053</t>
+        </is>
+      </c>
       <c r="AB34" t="inlineStr">
         <is>
           <t>fe0b77cb-f2dd-4ba4-b684-d4ecf9d4a053</t>
@@ -2834,6 +2939,11 @@
       <c r="W35" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>a7a77dd9-2c48-4420-8555-24aab9d0520c</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -3063,6 +3173,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>014ddb56-1613-49f0-9e34-a5e1f6c785fe</t>
+        </is>
+      </c>
       <c r="AB39" t="inlineStr">
         <is>
           <t>014ddb56-1613-49f0-9e34-a5e1f6c785fe</t>
@@ -3130,6 +3245,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>8b30b6c0-0bc1-4441-8820-964886587202</t>
+        </is>
+      </c>
       <c r="AB40" t="inlineStr">
         <is>
           <t>8b30b6c0-0bc1-4441-8820-964886587202</t>
@@ -3192,6 +3312,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>1a628a44-4c66-4d94-b410-673005311f11</t>
+        </is>
+      </c>
       <c r="AB41" t="inlineStr">
         <is>
           <t>1a628a44-4c66-4d94-b410-673005311f11</t>
@@ -3254,6 +3379,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>912252eb-66d4-4874-abc8-0c9951b57b07</t>
+        </is>
+      </c>
       <c r="AB42" t="inlineStr">
         <is>
           <t>912252eb-66d4-4874-abc8-0c9951b57b07</t>
@@ -3316,6 +3446,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>78755529-5600-440c-8380-ad656059ff13</t>
+        </is>
+      </c>
       <c r="AB43" t="inlineStr">
         <is>
           <t>78755529-5600-440c-8380-ad656059ff13</t>
@@ -3383,6 +3518,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>3d784cd2-6e86-46a8-bbd0-6f0b4d5c473c</t>
+        </is>
+      </c>
       <c r="AB44" t="inlineStr">
         <is>
           <t>3d784cd2-6e86-46a8-bbd0-6f0b4d5c473c</t>
@@ -3450,6 +3590,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>97fdc64c-6825-4fbc-b64c-406c522a9288</t>
+        </is>
+      </c>
       <c r="AB45" t="inlineStr">
         <is>
           <t>97fdc64c-6825-4fbc-b64c-406c522a9288</t>
@@ -3517,6 +3662,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>4b9555c8-11ce-4fb0-af28-67c8956588ae</t>
+        </is>
+      </c>
       <c r="AB46" t="inlineStr">
         <is>
           <t>4b9555c8-11ce-4fb0-af28-67c8956588ae</t>
@@ -3584,6 +3734,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>cb6d3d00-45b4-40eb-8e80-dff09bade591</t>
+        </is>
+      </c>
       <c r="AB47" t="inlineStr">
         <is>
           <t>cb6d3d00-45b4-40eb-8e80-dff09bade591</t>
@@ -3649,6 +3804,11 @@
       <c r="W48" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>44cede5f-e666-42c2-b9ea-20ca0d73478e</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -11275,6 +11435,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>d14fb2bb-b9cb-4ac9-9db3-e052c90daa2f</t>
+        </is>
+      </c>
       <c r="AB132" t="inlineStr">
         <is>
           <t>d14fb2bb-b9cb-4ac9-9db3-e052c90daa2f</t>
@@ -11332,6 +11497,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>754287bc-eb16-4fb1-adf5-9ba198ef61bc</t>
+        </is>
+      </c>
       <c r="AB133" t="inlineStr">
         <is>
           <t>754287bc-eb16-4fb1-adf5-9ba198ef61bc</t>
@@ -11394,6 +11564,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>610d1988-6af6-4bcc-a947-eb4020bc3119</t>
+        </is>
+      </c>
       <c r="AB134" t="inlineStr">
         <is>
           <t>610d1988-6af6-4bcc-a947-eb4020bc3119</t>
@@ -11456,6 +11631,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>ffa2eb74-b7c8-48f6-b268-2882ba61fae0</t>
+        </is>
+      </c>
       <c r="AB135" t="inlineStr">
         <is>
           <t>ffa2eb74-b7c8-48f6-b268-2882ba61fae0</t>
@@ -11518,6 +11698,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>318177e8-8c06-4cfe-a628-4c3f588e36e9</t>
+        </is>
+      </c>
       <c r="AB136" t="inlineStr">
         <is>
           <t>318177e8-8c06-4cfe-a628-4c3f588e36e9</t>
@@ -11590,6 +11775,11 @@
           <t>After the initial grab use 3+4 to escape.</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>e9174a35-b2b1-40d7-8704-552434c99980</t>
+        </is>
+      </c>
       <c r="AB137" t="inlineStr">
         <is>
           <t>e9174a35-b2b1-40d7-8704-552434c99980</t>
@@ -11652,6 +11842,11 @@
           <t>Double Arm Face Buster is not additional damage to the Jaguar Driver, it add 5 points of damage.</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>61fbd176-0a6e-4368-89b2-fae51c957338</t>
+        </is>
+      </c>
       <c r="AB138" t="inlineStr">
         <is>
           <t>61fbd176-0a6e-4368-89b2-fae51c957338</t>
@@ -11714,6 +11909,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>e370e475-82e9-42c2-9dda-e815185d01ba</t>
+        </is>
+      </c>
       <c r="AB139" t="inlineStr">
         <is>
           <t>e370e475-82e9-42c2-9dda-e815185d01ba</t>
@@ -11781,6 +11981,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>d0dc416c-d281-41de-a830-391175b9c733</t>
+        </is>
+      </c>
       <c r="AB140" t="inlineStr">
         <is>
           <t>d0dc416c-d281-41de-a830-391175b9c733</t>
@@ -11838,6 +12043,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>c1efc095-a281-425f-89ef-e6a21a09748e</t>
+        </is>
+      </c>
       <c r="AB141" t="inlineStr">
         <is>
           <t>c1efc095-a281-425f-89ef-e6a21a09748e</t>
@@ -11900,6 +12110,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>ca3bdbfd-726c-4c6a-8a68-16d368d953de</t>
+        </is>
+      </c>
       <c r="AB142" t="inlineStr">
         <is>
           <t>ca3bdbfd-726c-4c6a-8a68-16d368d953de</t>
@@ -11962,6 +12177,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>576fbd03-9817-4433-aee9-a05fb2873ee9</t>
+        </is>
+      </c>
       <c r="AB143" t="inlineStr">
         <is>
           <t>576fbd03-9817-4433-aee9-a05fb2873ee9</t>
@@ -12024,6 +12244,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>bf90b650-01f4-4fc9-88b8-319864f95c86</t>
+        </is>
+      </c>
       <c r="AB144" t="inlineStr">
         <is>
           <t>bf90b650-01f4-4fc9-88b8-319864f95c86</t>
@@ -12086,6 +12311,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>9cb56a53-599f-4719-9b84-f7e40bb6afa8</t>
+        </is>
+      </c>
       <c r="AB145" t="inlineStr">
         <is>
           <t>9cb56a53-599f-4719-9b84-f7e40bb6afa8</t>
@@ -12148,6 +12378,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>c053f961-d2f8-4fbd-83ae-34fca200b9b7</t>
+        </is>
+      </c>
       <c r="AB146" t="inlineStr">
         <is>
           <t>c053f961-d2f8-4fbd-83ae-34fca200b9b7</t>
@@ -12225,6 +12460,11 @@
           <t>Escape with 1 if the multi was started with 1+3 and 2 if the multi was started with 2+4.</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>8a657c3c-5962-4744-8afb-8db34e185b60</t>
+        </is>
+      </c>
       <c r="AB147" t="inlineStr">
         <is>
           <t>8a657c3c-5962-4744-8afb-8db34e185b60</t>
@@ -12287,6 +12527,11 @@
           <t>Escape with 1 if the multi was started with 1+3 and 2 if the multi was started with 2+4.</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>e9b59331-5359-43c8-a2fe-c2f1c768010e</t>
+        </is>
+      </c>
       <c r="AB148" t="inlineStr">
         <is>
           <t>e9b59331-5359-43c8-a2fe-c2f1c768010e</t>
@@ -12349,6 +12594,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>a35b6adb-c2ae-4dcc-8c1c-e89ddf41df28</t>
+        </is>
+      </c>
       <c r="AB149" t="inlineStr">
         <is>
           <t>a35b6adb-c2ae-4dcc-8c1c-e89ddf41df28</t>
@@ -12411,6 +12661,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>a076bd88-cfd9-4b82-b29b-751f8994df70</t>
+        </is>
+      </c>
       <c r="AB150" t="inlineStr">
         <is>
           <t>a076bd88-cfd9-4b82-b29b-751f8994df70</t>
@@ -12473,6 +12728,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>897562ea-11c8-48e1-bdd7-3508028d9455</t>
+        </is>
+      </c>
       <c r="AB151" t="inlineStr">
         <is>
           <t>897562ea-11c8-48e1-bdd7-3508028d9455</t>
@@ -12535,6 +12795,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>0499e709-28d1-44ad-884c-143bf75b7436</t>
+        </is>
+      </c>
       <c r="AB152" t="inlineStr">
         <is>
           <t>0499e709-28d1-44ad-884c-143bf75b7436</t>
@@ -12597,6 +12862,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>988107cd-c43e-41b1-bec3-f6450eebd275</t>
+        </is>
+      </c>
       <c r="AB153" t="inlineStr">
         <is>
           <t>988107cd-c43e-41b1-bec3-f6450eebd275</t>
@@ -12659,6 +12929,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>54aa2be5-501e-441f-b759-e6eaa8b2c7aa</t>
+        </is>
+      </c>
       <c r="AB154" t="inlineStr">
         <is>
           <t>54aa2be5-501e-441f-b759-e6eaa8b2c7aa</t>
@@ -12721,6 +12996,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>e36e2276-3cc6-43b4-bef5-0d88f962c067</t>
+        </is>
+      </c>
       <c r="AB155" t="inlineStr">
         <is>
           <t>e36e2276-3cc6-43b4-bef5-0d88f962c067</t>
@@ -12783,6 +13063,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>91806b57-15f2-453a-9e66-6e9265eb3f74</t>
+        </is>
+      </c>
       <c r="AB156" t="inlineStr">
         <is>
           <t>91806b57-15f2-453a-9e66-6e9265eb3f74</t>
@@ -12845,6 +13130,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>0d22dd12-3fab-495f-bd30-0dd66be69ec9</t>
+        </is>
+      </c>
       <c r="AB157" t="inlineStr">
         <is>
           <t>0d22dd12-3fab-495f-bd30-0dd66be69ec9</t>
@@ -12907,6 +13197,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>0b34d2a0-d07c-4603-9984-9e48ffa8b289</t>
+        </is>
+      </c>
       <c r="AB158" t="inlineStr">
         <is>
           <t>0b34d2a0-d07c-4603-9984-9e48ffa8b289</t>
@@ -12969,6 +13264,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>3a88bc91-07bf-4196-bbfc-65d00fdc5cdb</t>
+        </is>
+      </c>
       <c r="AB159" t="inlineStr">
         <is>
           <t>3a88bc91-07bf-4196-bbfc-65d00fdc5cdb</t>
@@ -13031,6 +13331,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>88d1f06b-09b4-4f3b-b26f-6b7eb09839b9</t>
+        </is>
+      </c>
       <c r="AB160" t="inlineStr">
         <is>
           <t>88d1f06b-09b4-4f3b-b26f-6b7eb09839b9</t>
@@ -13098,6 +13403,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>21a93725-b013-4fd7-b6a0-53b29c951345</t>
+        </is>
+      </c>
       <c r="AB161" t="inlineStr">
         <is>
           <t>21a93725-b013-4fd7-b6a0-53b29c951345</t>
@@ -13165,6 +13475,11 @@
           <t>If grabbed from the side or back then Cannonball will be the 1st part of the Multi Throw.</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>e5cfb3e7-d8eb-43a9-95a5-78b47376b89c</t>
+        </is>
+      </c>
       <c r="AB162" t="inlineStr">
         <is>
           <t>e5cfb3e7-d8eb-43a9-95a5-78b47376b89c</t>
@@ -13227,6 +13542,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>d29031f4-9c39-4518-8ca7-d1d579f731d3</t>
+        </is>
+      </c>
       <c r="AB163" t="inlineStr">
         <is>
           <t>d29031f4-9c39-4518-8ca7-d1d579f731d3</t>
@@ -13284,6 +13604,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>cf747642-f5e0-4884-9c87-bf258ea86c4c</t>
+        </is>
+      </c>
       <c r="AB164" t="inlineStr">
         <is>
           <t>cf747642-f5e0-4884-9c87-bf258ea86c4c</t>
@@ -13346,6 +13671,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>90ec3fb9-f4d7-421a-99e2-e37e4a49ce00</t>
+        </is>
+      </c>
       <c r="AB165" t="inlineStr">
         <is>
           <t>90ec3fb9-f4d7-421a-99e2-e37e4a49ce00</t>
@@ -13408,6 +13738,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>334b113e-5fa6-4350-8c7f-d1443e15e6b7</t>
+        </is>
+      </c>
       <c r="AB166" t="inlineStr">
         <is>
           <t>334b113e-5fa6-4350-8c7f-d1443e15e6b7</t>
@@ -13470,6 +13805,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>58f13036-58ee-4611-a14d-d783777422a0</t>
+        </is>
+      </c>
       <c r="AB167" t="inlineStr">
         <is>
           <t>58f13036-58ee-4611-a14d-d783777422a0</t>
@@ -13532,6 +13872,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>f7973f34-41fe-4bf5-95c3-8fb79ee2452d</t>
+        </is>
+      </c>
       <c r="AB168" t="inlineStr">
         <is>
           <t>f7973f34-41fe-4bf5-95c3-8fb79ee2452d</t>
@@ -13594,6 +13939,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>0515905e-bcfb-496f-bbfc-01dedb07caa4</t>
+        </is>
+      </c>
       <c r="AB169" t="inlineStr">
         <is>
           <t>0515905e-bcfb-496f-bbfc-01dedb07caa4</t>
@@ -13656,6 +14006,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>fefe8385-3ffe-4743-8071-1a48c86080c5</t>
+        </is>
+      </c>
       <c r="AB170" t="inlineStr">
         <is>
           <t>fefe8385-3ffe-4743-8071-1a48c86080c5</t>
@@ -13716,6 +14071,11 @@
       <c r="W171" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>cd229188-1f00-4e2c-beb7-0ecdab35b8dc</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr">
@@ -13935,6 +14295,11 @@
           <t>hhmmhLLLmM</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>540396d1-00a1-4033-9fce-7dbbcf91bebf</t>
+        </is>
+      </c>
       <c r="AB175" t="inlineStr">
         <is>
           <t>540396d1-00a1-4033-9fce-7dbbcf91bebf</t>
@@ -13987,6 +14352,11 @@
           <t>hhmmhLLLmh</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>53b541e0-d1fa-4602-8e8e-198dc6d57441</t>
+        </is>
+      </c>
       <c r="AB176" t="inlineStr">
         <is>
           <t>53b541e0-d1fa-4602-8e8e-198dc6d57441</t>
@@ -14039,6 +14409,11 @@
           <t>hhmmhmLLmM</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>d76e55af-5e37-469f-b459-858d5c452608</t>
+        </is>
+      </c>
       <c r="AB177" t="inlineStr">
         <is>
           <t>d76e55af-5e37-469f-b459-858d5c452608</t>
@@ -14091,6 +14466,11 @@
           <t>hhmmhmLLmh</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>10ceada9-d82e-41bd-b56c-5a3fa1400921</t>
+        </is>
+      </c>
       <c r="AB178" t="inlineStr">
         <is>
           <t>10ceada9-d82e-41bd-b56c-5a3fa1400921</t>
@@ -14143,6 +14523,11 @@
           <t>hhmmhmLLlthrow</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>5c5c8a42-acd0-4b4b-88f6-39a67110202e</t>
+        </is>
+      </c>
       <c r="AB179" t="inlineStr">
         <is>
           <t>5c5c8a42-acd0-4b4b-88f6-39a67110202e</t>
@@ -14195,6 +14580,11 @@
           <t>hmmhLLLmM</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>47c1d8e6-c95b-4542-b264-13a374b2c050</t>
+        </is>
+      </c>
       <c r="AB180" t="inlineStr">
         <is>
           <t>47c1d8e6-c95b-4542-b264-13a374b2c050</t>
@@ -14247,6 +14637,11 @@
           <t>hmmhLLLmh</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>76d4a800-1555-4b0e-a6b7-bdcb47516018</t>
+        </is>
+      </c>
       <c r="AB181" t="inlineStr">
         <is>
           <t>76d4a800-1555-4b0e-a6b7-bdcb47516018</t>
@@ -14299,6 +14694,11 @@
           <t>hmmhmLLmM</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>d3e32834-6f80-4957-ac5b-a1be0e260a44</t>
+        </is>
+      </c>
       <c r="AB182" t="inlineStr">
         <is>
           <t>d3e32834-6f80-4957-ac5b-a1be0e260a44</t>
@@ -14351,6 +14751,11 @@
           <t>hmmhmLLmh</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>3de5ed24-6134-418b-ba3e-f25a1039677a</t>
+        </is>
+      </c>
       <c r="AB183" t="inlineStr">
         <is>
           <t>3de5ed24-6134-418b-ba3e-f25a1039677a</t>
@@ -14401,6 +14806,11 @@
       <c r="U184" t="inlineStr">
         <is>
           <t>hmmhmLLlthrow</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>9aa5afc6-6646-4750-b84c-b3114de16321</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr">
